--- a/reports/Debug-snowbowl-20251216/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251216/Week Total (Prior Year)_Visits.xlsx
@@ -714,10 +714,10 @@
         <v>45642</v>
       </c>
       <c r="C22" s="2">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,10 +725,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="C23" s="2">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>6</v>
@@ -742,10 +742,10 @@
         <v>45644</v>
       </c>
       <c r="C24" s="2">
-        <v>1245</v>
+        <v>70</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +756,10 @@
         <v>45645</v>
       </c>
       <c r="C25" s="2">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="C26" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>6</v>
@@ -781,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45646</v>
+        <v>45648</v>
       </c>
       <c r="C27" s="2">
-        <v>929</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>6</v>
@@ -795,10 +795,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45647</v>
+        <v>45648</v>
       </c>
       <c r="C28" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>6</v>
@@ -809,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45647</v>
+        <v>45643</v>
       </c>
       <c r="C29" s="2">
-        <v>1531</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,10 +823,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45648</v>
+        <v>45644</v>
       </c>
       <c r="C30" s="2">
-        <v>16</v>
+        <v>547</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>6</v>
@@ -837,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C31" s="2">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45642</v>
+        <v>45646</v>
       </c>
       <c r="C32" s="2">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -865,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45643</v>
+        <v>45647</v>
       </c>
       <c r="C33" s="2">
-        <v>1155</v>
+        <v>890</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45643</v>
+        <v>45642</v>
       </c>
       <c r="C34" s="2">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,10 +893,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45644</v>
+        <v>45642</v>
       </c>
       <c r="C35" s="2">
-        <v>2</v>
+        <v>602</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>6</v>
@@ -907,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="C36" s="2">
         <v>75</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C37" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>6</v>
@@ -935,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C38" s="2">
-        <v>936</v>
+        <v>607</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45646</v>
+        <v>45645</v>
       </c>
       <c r="C39" s="2">
-        <v>117</v>
+        <v>1230</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -963,10 +963,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45647</v>
+        <v>45648</v>
       </c>
       <c r="C40" s="2">
-        <v>5</v>
+        <v>903</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>6</v>
@@ -977,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45642</v>
+        <v>45648</v>
       </c>
       <c r="C41" s="2">
-        <v>83</v>
+        <v>1613</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -991,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45644</v>
+        <v>45642</v>
       </c>
       <c r="C42" s="2">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,10 +1005,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45644</v>
+        <v>45643</v>
       </c>
       <c r="C43" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>6</v>
@@ -1019,13 +1019,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45645</v>
+        <v>45644</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>1245</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45647</v>
+        <v>45645</v>
       </c>
       <c r="C45" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C46" s="2">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>6</v>
@@ -1061,10 +1061,10 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C47" s="2">
-        <v>9</v>
+        <v>929</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>6</v>
@@ -1075,10 +1075,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45643</v>
+        <v>45647</v>
       </c>
       <c r="C48" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>6</v>
@@ -1089,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45644</v>
+        <v>45647</v>
       </c>
       <c r="C49" s="2">
-        <v>547</v>
+        <v>1531</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,10 +1103,10 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45646</v>
+        <v>45648</v>
       </c>
       <c r="C50" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>6</v>
@@ -1117,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45646</v>
+        <v>45648</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>224</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45647</v>
+        <v>45642</v>
       </c>
       <c r="C52" s="2">
-        <v>890</v>
+        <v>71</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>6</v>
@@ -1145,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="C53" s="2">
-        <v>6</v>
+        <v>1155</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="C54" s="2">
-        <v>602</v>
+        <v>50</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>45644</v>
       </c>
       <c r="C55" s="2">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,7 +1190,7 @@
         <v>45645</v>
       </c>
       <c r="C56" s="2">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>6</v>
@@ -1201,10 +1201,10 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="C57" s="2">
-        <v>607</v>
+        <v>3</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>6</v>
@@ -1215,10 +1215,10 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="C58" s="2">
-        <v>1230</v>
+        <v>936</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>7</v>
@@ -1229,13 +1229,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C59" s="2">
-        <v>903</v>
+        <v>117</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1243,13 +1243,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="C60" s="2">
-        <v>1613</v>
+        <v>5</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
